--- a/نرخ_تاکسی_بار_لنگرود_۱۴۰۴.xlsx
+++ b/نرخ_تاکسی_بار_لنگرود_۱۴۰۴.xlsx
@@ -7,33 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="نرخ شهری" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="کرایه بین‌شهری" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="(الف)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="(ب)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="(پ)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="(ت)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="(ج)" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="(ح)" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="(خ)" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="(د)" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="(ر)" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="(ز)" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="(س)" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="(ش)" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="(ص)" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="(ض)" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="(ع)" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="(ف)" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="(ق)" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="(ک)" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="(گ)" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="(ل)" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="(م)" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="(ن)" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="(و)" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="(هـ)" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="(ی)" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="کرایه بین‌شهری" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -43,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -57,14 +31,11 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
       <sz val="12"/>
     </font>
     <font>
       <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="4">
@@ -76,14 +47,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
-        <bgColor rgb="00D9E1F2"/>
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8E8E8"/>
-        <bgColor rgb="00E8E8E8"/>
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -105,15 +76,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -121,18 +92,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -499,2161 +458,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>«نرخ پیشنهادی 1» تاکسی بار شهرستان لنگرود در سال 1404</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>ردیف</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>نوع بار</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>پیکان</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>مزدا 1600</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>نیسان</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>ردیف</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>مقصد</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>پیکان</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>مزدا 1600</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>نیسان</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>حمل بار شهری</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>250000</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>350000</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>حمل اثاثیه منزل و وزن بیش از حد قانونی</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>400000</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>600000</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>800000</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>جریمه حمل بار به عهده صاحب بار می باشد.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A7:E7"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>(د)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>مقصد</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>پیکان</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>مزدا 1600</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>نیسان</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>دیلمان سختی راه</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>2400000</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>2700000</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>3000000</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>دیزین داخل محل</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>380000</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>520000</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>680000</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>دریا کنار</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>450000</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>610000</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>780000</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>درگاه رودبنه</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>700000</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>890000</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>1080000</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>داخل رودبنه</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>610000</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>800000</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>دهشال</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>730000</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>910000</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>1100000</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>دیرین</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>380000</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>520000</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>680000</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>دیوشل محل</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>310000</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>430000</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>580000</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>دهسر کیاسر</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>630000</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>810000</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>دکانور</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="n">
-        <v>330000</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>450000</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>600000</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>درویشانبر</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="n">
-        <v>250000</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>350000</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>دریاسر یعقوبیه</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="n">
-        <v>300000</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>430000</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>570000</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>دستک</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="n">
-        <v>720000</v>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>890000</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>1080000</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>دهبنه</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="n">
-        <v>750000</v>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>950000</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>1150000</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>دهکانه</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="n">
-        <v>850000</v>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>1050000</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>1250000</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>(ر)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>مقصد</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>پیکان</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>مزدا 1600</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>نیسان</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>رامدشت رودسر</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>520000</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>700000</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>880000</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>رانکوه</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>680000</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>860000</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>1050000</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>رامسر</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>1400000</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>1600000</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>رودبار</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>2200000</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>2400000</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>2700000</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>رحیم آباد</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>820000</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>1250000</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>رضوانشهر</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>2200000</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>2450000</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>2700000</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>رودسر شهرک</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>520000</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>700000</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>880000</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>راهدار کومه</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>420000</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>570000</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>730000</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>رشت</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>1400000</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>1600000</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>رودسر</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="n">
-        <v>500000</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>670000</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>850000</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>رودبنه بالا محله</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="n">
-        <v>560000</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>750000</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>940000</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>رودبنه پایین محله</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="n">
-        <v>570000</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>760000</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>950000</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>رشت شهر صنعتی</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="n">
-        <v>1250000</v>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>1450000</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>1650000</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>رستم آباد</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="n">
-        <v>1900000</v>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>2150000</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>2400000</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>رضا محله رودسر</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="n">
-        <v>570000</v>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>760000</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>950000</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>(ز)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>مقصد</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>پیکان</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>مزدا 1600</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>نیسان</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>زرد آب محله</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>250000</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>350000</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>زالکبر</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>680000</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>860000</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>1050000</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>زیبا کنار</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>1150000</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>1350000</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>1550000</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>زمیدان لاهیجان</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>650000</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>820000</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>زیاز</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>1850000</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>2050000</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>2350000</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>زنجان</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>520000</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>560000</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>610000</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>(س)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>مقصد</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>پیکان</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>مزدا 1600</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>نیسان</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>سیاهکل</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>770000</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>970000</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>1200000</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>ساری</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>5500000</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>6500000</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>ساوه</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>490000</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>530000</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>580000</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>سنگر</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>1100000</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>1300000</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>1550000</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>سراوان</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>1300000</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>1700000</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>سمنان</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>800000</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>860000</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>950000</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>سیگارود</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>400000</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>550000</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>700000</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>سراجار</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>500000</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>670000</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>850000</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>سرچشمه لاهیجان</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>900000</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>1100000</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>1300000</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>سادات</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="n">
-        <v>430000</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>580000</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>750000</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>سادات محله بارکوسرا</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="n">
-        <v>500000</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>670000</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>850000</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>سیاهکلده</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="n">
-        <v>420000</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>570000</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>740000</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>سیاهکوه</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="n">
-        <v>330000</v>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>450000</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>600000</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>سوستان لاهیجان</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="n">
-        <v>560000</v>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>750000</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>940000</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>سیاهکلده رود</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="n">
-        <v>850000</v>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>1050000</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>1250000</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>سحر خیز رود</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="n">
-        <v>550000</v>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>720000</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>900000</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>سلمانسرای</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n">
-        <v>380000</v>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>520000</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>680000</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>سمیر کوه املش</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n">
-        <v>420000</v>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>580000</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>750000</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>سادات محله رامسر</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="n">
-        <v>1300000</v>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>1700000</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>سیب داربن املش</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="n">
-        <v>600000</v>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>780000</v>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>960000</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>سد لنگ</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="n">
-        <v>800000</v>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>860000</v>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>950000</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>سفید آب</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="C25" s="4" t="n">
-        <v>1400000</v>
-      </c>
-      <c r="D25" s="4" t="n">
-        <v>1650000</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>سوخته سر لاهیجان</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="n">
-        <v>690000</v>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>870000</v>
-      </c>
-      <c r="D26" s="4" t="n">
-        <v>1100000</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>سوخته کوه</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="n">
-        <v>640000</v>
-      </c>
-      <c r="C27" s="4" t="n">
-        <v>820000</v>
-      </c>
-      <c r="D27" s="4" t="n">
-        <v>1000000</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>(ش)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>مقصد</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>پیکان</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>مزدا 1600</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>نیسان</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>شفت</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>1700000</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>1950000</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>شلمان</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>380000</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>520000</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>680000</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>شرفشاده</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>750000</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>950000</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>1150000</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>شیرجو پشت</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>550000</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>720000</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>920000</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>شیخعلی کلاه</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>660000</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>860000</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>1050000</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>شب خوس لات</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>700000</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>880000</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>1080000</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>شکر کش</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>550000</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>720000</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>920000</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>شهدای باغ صدر محله</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>280000</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>390000</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>550000</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>شکل لاهیجان</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>800000</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>1250000</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>شیخانبر</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="n">
-        <v>450000</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>610000</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>790000</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>شکارکلاه</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="n">
-        <v>520000</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>700000</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>880000</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>شمسترود</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="n">
-        <v>660000</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>860000</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>1050000</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>(ص)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>مقصد</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>پیکان</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>مزدا 1600</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>نیسان</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>صومعه سرا</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>1700000</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>1900000</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>2100000</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>صدر محله</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>400000</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>550000</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>700000</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>صحنه سرا</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>500000</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>670000</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>850000</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>صلاح جان واجارگاه</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>850000</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>1050000</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>1250000</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>صقلیه</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>440000</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>600000</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>780000</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>صدر محله حسن آباد</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>440000</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>600000</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>780000</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>(ض)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>مقصد</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>پیکان</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>مزدا 1600</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>نیسان</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>ضیابر</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>2200000</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>2400000</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>(ع)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>مقصد</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>پیکان</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>مزدا 1600</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>نیسان</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>عباس آباد</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>1950000</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>2250000</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>2600000</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>علمدده</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>400000</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>450000</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>510000</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>(ف)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>مقصد</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>پیکان</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>مزدا 1600</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>نیسان</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>فومن</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>1600000</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>1800000</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>2000000</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>فتیده</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>380000</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>520000</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>680000</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>فیش پشته</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>600000</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>780000</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>970000</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>فشازده</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>760000</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>960000</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>1150000</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>فریدون کنار</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>4500000</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>4850000</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>5350000</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>(ق)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>مقصد</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>پیکان</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>مزدا 1600</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>نیسان</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>قزوین</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>3300000</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>3700000</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>4200000</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>قم</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>5500000</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>6000000</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>قاسم آباد کلاچای</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>950000</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>1150000</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>1350000</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>قاضی محله شلمان</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>380000</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>520000</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>680000</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>قائم شهر</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>5200000</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>5700000</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>6200000</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>قرچک</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>4800000</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>5300000</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>5800000</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>قوچان</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>10500000</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>11500000</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>12500000</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>قصاب محله آبشار</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>450000</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>610000</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>780000</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2672,7 +476,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>(الف)</t>
         </is>
@@ -3409,7 +1213,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="7" t="inlineStr">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>(ب)</t>
         </is>
@@ -3804,7 +1608,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="7" t="inlineStr">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>(پ)</t>
         </is>
@@ -4180,7 +1984,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="7" t="inlineStr">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>(ت)</t>
         </is>
@@ -4499,7 +2303,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="7" t="inlineStr">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>(ج)</t>
         </is>
@@ -5065,7 +2869,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="7" t="inlineStr">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>(ح)</t>
         </is>
@@ -5251,7 +3055,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="7" t="inlineStr">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>(خ)</t>
         </is>
@@ -5494,7 +3298,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="7" t="inlineStr">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>(د)</t>
         </is>
@@ -5813,7 +3617,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="7" t="inlineStr">
+      <c r="A178" s="2" t="inlineStr">
         <is>
           <t>(ر)</t>
         </is>
@@ -6132,7 +3936,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="7" t="inlineStr">
+      <c r="A196" s="2" t="inlineStr">
         <is>
           <t>(ز)</t>
         </is>
@@ -6280,7 +4084,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="7" t="inlineStr">
+      <c r="A205" s="2" t="inlineStr">
         <is>
           <t>(س)</t>
         </is>
@@ -6770,7 +4574,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="7" t="inlineStr">
+      <c r="A232" s="2" t="inlineStr">
         <is>
           <t>(ش)</t>
         </is>
@@ -7032,7 +4836,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="7" t="inlineStr">
+      <c r="A247" s="2" t="inlineStr">
         <is>
           <t>(ص)</t>
         </is>
@@ -7180,7 +4984,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="7" t="inlineStr">
+      <c r="A256" s="2" t="inlineStr">
         <is>
           <t>(ض)</t>
         </is>
@@ -7233,7 +5037,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="7" t="inlineStr">
+      <c r="A260" s="2" t="inlineStr">
         <is>
           <t>(ع)</t>
         </is>
@@ -7305,7 +5109,7 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="7" t="inlineStr">
+      <c r="A265" s="2" t="inlineStr">
         <is>
           <t>(ف)</t>
         </is>
@@ -7434,7 +5238,7 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="7" t="inlineStr">
+      <c r="A273" s="2" t="inlineStr">
         <is>
           <t>(ق)</t>
         </is>
@@ -7620,7 +5424,7 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="7" t="inlineStr">
+      <c r="A284" s="2" t="inlineStr">
         <is>
           <t>(ک)</t>
         </is>
@@ -8433,7 +6237,7 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="7" t="inlineStr">
+      <c r="A328" s="2" t="inlineStr">
         <is>
           <t>(گ)</t>
         </is>
@@ -8562,7 +6366,7 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" s="7" t="inlineStr">
+      <c r="A336" s="2" t="inlineStr">
         <is>
           <t>(ل)</t>
         </is>
@@ -9090,7 +6894,7 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" s="7" t="inlineStr">
+      <c r="A365" s="2" t="inlineStr">
         <is>
           <t>(م)</t>
         </is>
@@ -9466,7 +7270,7 @@
       </c>
     </row>
     <row r="386">
-      <c r="A386" s="7" t="inlineStr">
+      <c r="A386" s="2" t="inlineStr">
         <is>
           <t>(ن)</t>
         </is>
@@ -9728,7 +7532,7 @@
       </c>
     </row>
     <row r="401">
-      <c r="A401" s="7" t="inlineStr">
+      <c r="A401" s="2" t="inlineStr">
         <is>
           <t>(و)</t>
         </is>
@@ -9838,7 +7642,7 @@
       </c>
     </row>
     <row r="408">
-      <c r="A408" s="7" t="inlineStr">
+      <c r="A408" s="2" t="inlineStr">
         <is>
           <t>(هـ)</t>
         </is>
@@ -9910,7 +7714,7 @@
       </c>
     </row>
     <row r="413">
-      <c r="A413" s="7" t="inlineStr">
+      <c r="A413" s="2" t="inlineStr">
         <is>
           <t>(ی)</t>
         </is>
@@ -9993,4704 +7797,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D44"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>(ک)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>مقصد</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>پیکان</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>مزدا 1600</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>نیسان</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>کهنه گویه رودسر</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>720000</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>890000</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>1080000</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>کمال پشته کالشکلام</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>450000</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>610000</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>770000</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>کلان کلایه رودسر</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>680000</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>860000</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>1050000</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>کجلام</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>660000</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>830000</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>کنف گوراب رودبنه</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>600000</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>780000</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>970000</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>کوشالشاه</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>380000</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>520000</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>680000</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>کش کن محله</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>500000</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>670000</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>850000</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>کیسم</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>790000</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>970000</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>1200000</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>کلدره</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>550000</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>740000</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>920000</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>کهنه گوراب املش</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="n">
-        <v>450000</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>610000</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>770000</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>کیور چال انزلی</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>2250000</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>2500000</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>کورنده</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="n">
-        <v>580000</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>750000</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>930000</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>کانالم رامسر</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="n">
-        <v>1300000</v>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>1700000</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>کوره کانیجار</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="n">
-        <v>750000</v>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>950000</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>1150000</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>کولاک محله سلوش</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="n">
-        <v>420000</v>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>550000</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>730000</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>کومله چهار راه</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="n">
-        <v>350000</v>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>470000</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>640000</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>کلسفید</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n">
-        <v>430000</v>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>570000</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>750000</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>کرسگ محله املش</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n">
-        <v>720000</v>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>890000</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>1080000</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>کوتاب زرمیخ</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="n">
-        <v>1900000</v>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>2100000</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>2300000</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>کارواسرا</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="n">
-        <v>450000</v>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>610000</v>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>780000</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>کرگان</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="n">
-        <v>750000</v>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>820000</v>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>900000</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>کسگر محله</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="n">
-        <v>550000</v>
-      </c>
-      <c r="C25" s="4" t="n">
-        <v>730000</v>
-      </c>
-      <c r="D25" s="4" t="n">
-        <v>910000</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>کل رودبار سیاهکل</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="n">
-        <v>650000</v>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>820000</v>
-      </c>
-      <c r="D26" s="4" t="n">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>گورندان لاهیجان</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="n">
-        <v>550000</v>
-      </c>
-      <c r="C27" s="4" t="n">
-        <v>730000</v>
-      </c>
-      <c r="D27" s="4" t="n">
-        <v>910000</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>کوکه سیاهکل</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="n">
-        <v>800000</v>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="D28" s="4" t="n">
-        <v>1250000</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>کالش کلام</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="n">
-        <v>450000</v>
-      </c>
-      <c r="C29" s="4" t="n">
-        <v>610000</v>
-      </c>
-      <c r="D29" s="4" t="n">
-        <v>780000</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>کاچورا سر</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="n">
-        <v>350000</v>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>470000</v>
-      </c>
-      <c r="D30" s="4" t="n">
-        <v>640000</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>کاویه (امام ده)</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="n">
-        <v>600000</v>
-      </c>
-      <c r="C31" s="4" t="n">
-        <v>780000</v>
-      </c>
-      <c r="D31" s="4" t="n">
-        <v>970000</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>کهنه رود پشت</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="n">
-        <v>700000</v>
-      </c>
-      <c r="C32" s="4" t="n">
-        <v>890000</v>
-      </c>
-      <c r="D32" s="4" t="n">
-        <v>1100000</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>کلاچای</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="n">
-        <v>700000</v>
-      </c>
-      <c r="C33" s="4" t="n">
-        <v>890000</v>
-      </c>
-      <c r="D33" s="4" t="n">
-        <v>1100000</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>کرج</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="n">
-        <v>4200000</v>
-      </c>
-      <c r="C34" s="4" t="n">
-        <v>4600000</v>
-      </c>
-      <c r="D34" s="4" t="n">
-        <v>5000000</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>کوچصفهان</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="n">
-        <v>930000</v>
-      </c>
-      <c r="C35" s="4" t="n">
-        <v>1100000</v>
-      </c>
-      <c r="D35" s="4" t="n">
-        <v>1300000</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>کیاشهر</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="n">
-        <v>950000</v>
-      </c>
-      <c r="C36" s="4" t="n">
-        <v>1150000</v>
-      </c>
-      <c r="D36" s="4" t="n">
-        <v>1350000</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>کومله</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="n">
-        <v>350000</v>
-      </c>
-      <c r="C37" s="4" t="n">
-        <v>470000</v>
-      </c>
-      <c r="D37" s="4" t="n">
-        <v>640000</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>کاشان</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="n">
-        <v>6800000</v>
-      </c>
-      <c r="C38" s="4" t="n">
-        <v>7400000</v>
-      </c>
-      <c r="D38" s="4" t="n">
-        <v>8200000</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>کرمانشاه</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="n">
-        <v>8000000</v>
-      </c>
-      <c r="C39" s="4" t="n">
-        <v>8600000</v>
-      </c>
-      <c r="D39" s="4" t="n">
-        <v>9500000</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>کسما</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="n">
-        <v>1800000</v>
-      </c>
-      <c r="C40" s="4" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="D40" s="4" t="n">
-        <v>2200000</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>کلاردشت</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="n">
-        <v>3500000</v>
-      </c>
-      <c r="C41" s="4" t="n">
-        <v>4100000</v>
-      </c>
-      <c r="D41" s="4" t="n">
-        <v>4800000</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>کلارآباد</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="n">
-        <v>2400000</v>
-      </c>
-      <c r="C42" s="4" t="n">
-        <v>2700000</v>
-      </c>
-      <c r="D42" s="4" t="n">
-        <v>3050000</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>کوشال</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="n">
-        <v>550000</v>
-      </c>
-      <c r="C43" s="4" t="n">
-        <v>730000</v>
-      </c>
-      <c r="D43" s="4" t="n">
-        <v>910000</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>کوچگده آبنار</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="n">
-        <v>500000</v>
-      </c>
-      <c r="C44" s="4" t="n">
-        <v>670000</v>
-      </c>
-      <c r="D44" s="4" t="n">
-        <v>850000</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>(گ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>مقصد</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>پیکان</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>مزدا 1600</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>نیسان</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>گلبافسرا بازارده</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>320000</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>440000</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>580000</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>کرکرود املش</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>740000</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>910000</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>1100000</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>کالش خاله</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>380000</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>520000</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>680000</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>گیلده</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>780000</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>1200000</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>گرمابدشت سختی راه</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>1800000</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>2200000</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>(ل)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>مقصد</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>پیکان</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>مزدا 1600</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>نیسان</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>لاهیجان</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>500000</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>670000</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>850000</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>لاهیجان بیجاربنه</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>500000</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>670000</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>850000</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>لشت نشا</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>900000</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>1050000</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>1200000</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>لوشان</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>2600000</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>3200000</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>لک موج املش</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>450000</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>610000</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>770000</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>لیلاکوه اول محل</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>430000</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>580000</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>750000</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>لیلا کوه بالا محل</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>420000</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>570000</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>740000</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>لبالستان بر خط</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>420000</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>570000</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>740000</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>لبالستان داخل محل</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>420000</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>570000</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>740000</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>لمیجان سیاهکل</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="n">
-        <v>770000</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>970000</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>1200000</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>لاهیجان حکومتی</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="n">
-        <v>500000</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>670000</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>850000</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>لات لیل</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="n">
-        <v>610000</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>790000</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>980000</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>لیل</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="n">
-        <v>650000</v>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>820000</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>لیسه رود</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="n">
-        <v>500000</v>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>670000</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>850000</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>لشه</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="n">
-        <v>540000</v>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>710000</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>890000</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>لو کلایه</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="n">
-        <v>360000</v>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>500000</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>660000</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>لونک سیاهکل</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n">
-        <v>2100000</v>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>2300000</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>2500000</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>لبارجدمه</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n">
-        <v>700000</v>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>870000</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>1050000</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>لشکاجان</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="n">
-        <v>610000</v>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>790000</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>980000</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>لوسه کلایه</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="n">
-        <v>900000</v>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>1100000</v>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>1300000</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>لات محله کومله</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="n">
-        <v>360000</v>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>500000</v>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>660000</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>لاکمه لاهیجان</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="n">
-        <v>590000</v>
-      </c>
-      <c r="C25" s="4" t="n">
-        <v>770000</v>
-      </c>
-      <c r="D25" s="4" t="n">
-        <v>960000</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>لوخ دستک</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="n">
-        <v>760000</v>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>950000</v>
-      </c>
-      <c r="D26" s="4" t="n">
-        <v>1150000</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>لاله رود رودسر</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="n">
-        <v>590000</v>
-      </c>
-      <c r="C27" s="4" t="n">
-        <v>770000</v>
-      </c>
-      <c r="D27" s="4" t="n">
-        <v>960000</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>لوشان</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="n">
-        <v>820000</v>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="D28" s="4" t="n">
-        <v>1200000</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>لبالمان</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="n">
-        <v>590000</v>
-      </c>
-      <c r="C29" s="4" t="n">
-        <v>770000</v>
-      </c>
-      <c r="D29" s="4" t="n">
-        <v>950000</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>(م)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>مقصد</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>پیکان</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>مزدا 1600</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>نیسان</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>محمود آباد</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>410000</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>450000</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>متل قو</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>2250000</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>2550000</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>2900000</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>منجیل</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>2400000</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>2700000</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>3000000</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>محسن آباد</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>760000</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>950000</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>1150000</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>موبندان</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>280000</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>390000</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>550000</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>متعلق محله ارباستان</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>470000</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>640000</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>820000</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>ملاط</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>340000</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>460000</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>630000</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>مریدان بر خط</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>440000</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>600000</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>780000</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>مالده سیاهکل</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>820000</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>1200000</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>ماچیان</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="n">
-        <v>790000</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>970000</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>1200000</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>مشکله</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="n">
-        <v>500000</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>670000</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>850000</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>ماسال شاندرمن</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="n">
-        <v>2100000</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>2300000</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>2500000</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>ماسوله</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="n">
-        <v>2200000</v>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>2400000</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>2600000</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>مراددهنده لاهیجان</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="n">
-        <v>590000</v>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>770000</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>960000</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>مبرک محله رودسر</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="n">
-        <v>520000</v>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>700000</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>880000</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>مشهد</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="n">
-        <v>11500000</v>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>13000000</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>15000000</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>مرزن آباد</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n">
-        <v>3200000</v>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>3600000</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>4000000</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>مریدان داخل محله</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n">
-        <v>440000</v>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>580000</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>760000</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>(ن)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>مقصد</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>پیکان</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>مزدا 1600</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>نیسان</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>نور</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>3650000</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>4050000</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>4550000</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>نوشهر</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>2800000</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>3150000</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>3550000</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>ناصر کیاده</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>700000</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>880000</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>1050000</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>نوشر</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>600000</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>780000</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>970000</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>نالکیاشر</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>470000</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>640000</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>820000</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>نشتارود</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>1800000</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>2050000</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>2350000</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>نیاکو</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>650000</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>820000</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>نخجیر کلایه</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>500000</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>670000</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>850000</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>ناصر سرای رودسر</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>550000</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>730000</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>910000</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>نقره ده آستانه</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="n">
-        <v>800000</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>1250000</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>نالکیاشر پایین محله</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="n">
-        <v>470000</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>640000</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>820000</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>نالکیاشر میان محله</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="n">
-        <v>470000</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>640000</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>820000</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>(و)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>مقصد</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>پیکان</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>مزدا 1600</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>نیسان</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>واجارگاه</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>800000</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>1250000</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>ورامین</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>520000</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>570000</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>620000</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>ولیسه داخل محل</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>420000</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>560000</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>730000</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>ولیسه بر خط</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>410000</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>560000</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>730000</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>(هـ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>مقصد</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>پیکان</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>مزدا 1600</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>نیسان</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>هشتپر طوالش</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>2900000</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>3300000</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>3700000</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>همدان</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>6200000</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>6900000</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>7600000</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>(ی)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>مقصد</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>پیکان</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>مزدا 1600</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>نیسان</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>یعقوبیه</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>330000</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>450000</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>600000</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D40"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>(الف)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>مقصد</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>پیکان</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>مزدا 1600</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>نیسان</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>آستارا</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>370000</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>430000</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>480000</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>آمل</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>475000</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>520000</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>570000</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>آستانه</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>700000</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>890000</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>1100000</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>آی بابا قزوین</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>300000</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>350000</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>400000</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>الوغ فک</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>330000</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>450000</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>600000</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>آهندان لاهیجان</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>690000</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>850000</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>1050000</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>آق محلی سرا</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>450000</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>610000</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>790000</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>اسالم</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>280000</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>320000</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>360000</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>انزلی</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>1600000</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>1800000</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>2000000</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>امام زاده هاشم</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="n">
-        <v>1450000</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>1650000</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>1900000</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>اوشیان چابکسر</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>1400000</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>املش</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="n">
-        <v>500000</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>670000</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>850000</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>ارباستان(اول محل)</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="n">
-        <v>500000</v>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>670000</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>850000</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>ارباستان(دوم محل)</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="n">
-        <v>500000</v>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>670000</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>850000</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>انبارسر کیاشهر</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="n">
-        <v>820000</v>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>1200000</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>اکبر آباد بهمنان</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="n">
-        <v>630000</v>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>810000</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>امیر بکنده</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>1700000</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>اسلام شهر شافاجی</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>1450000</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>اردبیل</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="n">
-        <v>530000</v>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>600000</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>680000</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>اطاقور</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="n">
-        <v>500000</v>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>670000</v>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>850000</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>استاد کلایه املش</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="n">
-        <v>500000</v>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>670000</v>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>850000</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>ایوان استخر</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="n">
-        <v>700000</v>
-      </c>
-      <c r="C25" s="4" t="n">
-        <v>880000</v>
-      </c>
-      <c r="D25" s="4" t="n">
-        <v>1050000</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>اسماعیل گوابر</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="n">
-        <v>700000</v>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>880000</v>
-      </c>
-      <c r="D26" s="4" t="n">
-        <v>1050000</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>امیر کیاسر</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="n">
-        <v>950000</v>
-      </c>
-      <c r="C27" s="4" t="n">
-        <v>1150000</v>
-      </c>
-      <c r="D27" s="4" t="n">
-        <v>1350000</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>ازیم سیاهل</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="n">
-        <v>720000</v>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>900000</v>
-      </c>
-      <c r="D28" s="4" t="n">
-        <v>1100000</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>اسیلی سختی راه</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="n">
-        <v>230000</v>
-      </c>
-      <c r="C29" s="4" t="n">
-        <v>260000</v>
-      </c>
-      <c r="D29" s="4" t="n">
-        <v>290000</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>ایلام</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="n">
-        <v>1100000</v>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="D30" s="4" t="n">
-        <v>1350000</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>امیر آباد</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="n">
-        <v>630000</v>
-      </c>
-      <c r="C31" s="4" t="n">
-        <v>800000</v>
-      </c>
-      <c r="D31" s="4" t="n">
-        <v>990000</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>اصفهان</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="n">
-        <v>840000</v>
-      </c>
-      <c r="C32" s="4" t="n">
-        <v>900000</v>
-      </c>
-      <c r="D32" s="4" t="n">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>اراک</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="n">
-        <v>840000</v>
-      </c>
-      <c r="C33" s="4" t="n">
-        <v>900000</v>
-      </c>
-      <c r="D33" s="4" t="n">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>املش بالنگ</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="n">
-        <v>640000</v>
-      </c>
-      <c r="C34" s="4" t="n">
-        <v>820000</v>
-      </c>
-      <c r="D34" s="4" t="n">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>املش البرز</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="n">
-        <v>640000</v>
-      </c>
-      <c r="C35" s="4" t="n">
-        <v>820000</v>
-      </c>
-      <c r="D35" s="4" t="n">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>آلمان لنگه سیسکو</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="n">
-        <v>730000</v>
-      </c>
-      <c r="C36" s="4" t="n">
-        <v>920000</v>
-      </c>
-      <c r="D36" s="4" t="n">
-        <v>1100000</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>آسیدر ناصر کیاده</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="n">
-        <v>750000</v>
-      </c>
-      <c r="C37" s="4" t="n">
-        <v>950000</v>
-      </c>
-      <c r="D37" s="4" t="n">
-        <v>1150000</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>آبشار قصاب محله</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="n">
-        <v>450000</v>
-      </c>
-      <c r="C38" s="4" t="n">
-        <v>610000</v>
-      </c>
-      <c r="D38" s="4" t="n">
-        <v>780000</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>احمد آباد رودسر</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="n">
-        <v>550000</v>
-      </c>
-      <c r="C39" s="4" t="n">
-        <v>730000</v>
-      </c>
-      <c r="D39" s="4" t="n">
-        <v>900000</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>املش ریسندگی</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="n">
-        <v>680000</v>
-      </c>
-      <c r="C40" s="4" t="n">
-        <v>860000</v>
-      </c>
-      <c r="D40" s="4" t="n">
-        <v>1050000</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>(ب)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>مقصد</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>پیکان</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>مزدا 1600</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>نیسان</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>بابل</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>500000</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>550000</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>600000</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>بابلسر از راه آمل</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>490000</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>540000</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>590000</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>بن کلایه</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>660000</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>650000</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>790000</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>بهشهر</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>670000</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>680000</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>750000</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>بارکوسرا</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>500000</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>670000</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>850000</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>بازکیا گوراب</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>600000</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>790000</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>970000</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>بالنگه املش</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>640000</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>820000</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>بازارده</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>320000</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>440000</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>580000</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>بوجایه لاهیجان</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>540000</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>720000</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>900000</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>بی بالان رحیم آباد</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="n">
-        <v>820000</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>1200000</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>بونکسر رحیم آباد</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="n">
-        <v>820000</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>1200000</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>بازارده گلباغ سر</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="n">
-        <v>320000</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>440000</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>580000</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>بالا لیل</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="n">
-        <v>650000</v>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>820000</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>بلوردکان</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="n">
-        <v>850000</v>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>1050000</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>1250000</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>بیجار گرما جان</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="n">
-        <v>640000</v>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>820000</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>بالا رود پشت</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="n">
-        <v>600000</v>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>780000</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>950000</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>بیجار بنه</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n">
-        <v>530000</v>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>700000</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>880000</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>بالارود لونک</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>2200000</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>2400000</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>بهمنان آخر</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="n">
-        <v>600000</v>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>780000</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>970000</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>(پ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>مقصد</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>پیکان</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>مزدا 1600</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>نیسان</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>پایین رود پشت</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>820000</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>1050000</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>1250000</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>پاپکیاده</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>400000</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>550000</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>700000</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>پلت کله</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>330000</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>450000</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>600000</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>پل زمانی</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>550000</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>730000</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>910000</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>پشته له له سر</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>440000</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>600000</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>780000</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>پیر بازار رشت</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>1350000</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>1550000</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>1750000</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>پروش پایین</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>600000</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>790000</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>970000</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>پاپکیاده آخر محله</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>450000</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>610000</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>780000</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>پونل رضوانشهر</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>2400000</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>2650000</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>2950000</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>پاشاکی پایین محله</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="n">
-        <v>900000</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>1100000</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>1350000</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>پل خوشحال</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="n">
-        <v>670000</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>860000</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>1050000</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>بهمنان اول</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="n">
-        <v>570000</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>760000</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>950000</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>پرشکوه پایین</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="n">
-        <v>380000</v>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>520000</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>680000</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>پرشکوه بالا</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="n">
-        <v>380000</v>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>520000</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>680000</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>پیرپشته چمخاله</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="n">
-        <v>420000</v>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>560000</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>720000</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>پاشاکی بالا</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="n">
-        <v>850000</v>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>1050000</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>1300000</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>پیر کوه</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n">
-        <v>2700000</v>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>3300000</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>پرش بالا</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n">
-        <v>650000</v>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>820000</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>1000000</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>(ت)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>مقصد</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>پیکان</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>مزدا 1600</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>نیسان</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>تنکابن</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>1700000</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>1900000</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>تهران</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>4600000</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>5500000</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>6500000</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>تمیجان رودسر</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>500000</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>670000</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>850000</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>تبریز</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>8000000</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>8600000</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>9500000</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>توتکی سیاهکل</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>1400000</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>تازه آباد لیسه رود</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>530000</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>700000</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>880000</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>تازه آباد جاف</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>500000</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>670000</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>850000</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>تپه</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>360000</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>500000</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>650000</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>توله لات رحیم آباد</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>950000</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>1100000</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>1300000</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>توت باغ محله نالکیاشهر</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="n">
-        <v>500000</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>670000</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>850000</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>ترنستان لاهیجان</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="n">
-        <v>530000</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>700000</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>880000</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>تاکستان قزوین</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="n">
-        <v>3600000</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>4000000</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>4500000</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>تازه آباد چوکا</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="n">
-        <v>2100000</v>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>2350000</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>2600000</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>تالش محله (داخل محله)</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="n">
-        <v>350000</v>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>470000</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>620000</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>توت ورزه</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="n">
-        <v>750000</v>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>950000</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>1150000</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>(ج)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>مقصد</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>پیکان</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>مزدا 1600</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>نیسان</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>جنگل سیستان</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>3350000</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>3750000</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>4200000</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>جور گوابر املش</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>740000</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>910000</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>1100000</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>جدانوکر</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>310000</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>530000</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>580000</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>جیر گوابر املش</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>740000</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>910000</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>1100000</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>جیر باغ</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>680000</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>860000</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>1050000</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>جمعه بازار</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>1600000</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>1800000</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>2000000</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>جیرده رشت</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>1350000</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>1550000</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>1750000</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>جعفر آباد رشت</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>1400000</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>چمخاله</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>380000</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>520000</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>680000</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>چالوس</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="n">
-        <v>2600000</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>2950000</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>3350000</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>چابکسر</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="n">
-        <v>1050000</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>1250000</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>1450000</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>چاف پایین</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="n">
-        <v>480000</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>650000</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>830000</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>چاف بالا</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="n">
-        <v>480000</v>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>650000</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>830000</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>چماستان</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="n">
-        <v>420000</v>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>580000</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>750000</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>چینیجان اول</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="n">
-        <v>450000</v>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>610000</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>780000</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>چینیجان محل</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="n">
-        <v>450000</v>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>610000</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>780000</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>چمندان</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n">
-        <v>570000</v>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>760000</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>950000</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>چهارده آستانه</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n">
-        <v>820000</v>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>1200000</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>چلارس املش</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="n">
-        <v>500000</v>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>670000</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>850000</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>چاف جیر رودسر</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="n">
-        <v>500000</v>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>670000</v>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>850000</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>چوکا انزلی</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="n">
-        <v>2100000</v>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>2350000</v>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>2600000</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>چاپارخانه انزلی</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="n">
-        <v>1350000</v>
-      </c>
-      <c r="C25" s="4" t="n">
-        <v>1550000</v>
-      </c>
-      <c r="D25" s="4" t="n">
-        <v>1750000</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>چایجان کلاچای</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="n">
-        <v>900000</v>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>1100000</v>
-      </c>
-      <c r="D26" s="4" t="n">
-        <v>1300000</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>چالکرود رامسر</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="n">
-        <v>1350000</v>
-      </c>
-      <c r="C27" s="4" t="n">
-        <v>1550000</v>
-      </c>
-      <c r="D27" s="4" t="n">
-        <v>1750000</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>چوشل لاهیجان</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="n">
-        <v>670000</v>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>860000</v>
-      </c>
-      <c r="D28" s="4" t="n">
-        <v>1050000</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>چمخاله شهرک</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="n">
-        <v>420000</v>
-      </c>
-      <c r="C29" s="4" t="n">
-        <v>560000</v>
-      </c>
-      <c r="D29" s="4" t="n">
-        <v>720000</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>چمخاله راهدار کومه</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="n">
-        <v>420000</v>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>560000</v>
-      </c>
-      <c r="D30" s="4" t="n">
-        <v>720000</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>چابکسر سرولات</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="C31" s="4" t="n">
-        <v>1400000</v>
-      </c>
-      <c r="D31" s="4" t="n">
-        <v>1600000</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>(ح)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>مقصد</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>پیکان</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>مزدا 1600</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>نیسان</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>حاجی سرا</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>470000</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>640000</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>820000</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>حسن بکنده</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>590000</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>760000</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>950000</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>حسن علی ده</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>790000</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>1200000</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>حاج ابراهیم ده</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>310000</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>430000</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>580000</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>حسن آباد صدر محله</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>450000</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>610000</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>780000</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>حسن سرا رودسر</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>610000</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>790000</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>980000</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>حسن رود انزلی</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>1450000</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>1650000</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>1850000</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>حسین آباد جاف</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>530000</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>700000</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>880000</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>(خ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>مقصد</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>پیکان</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>مزدا 1600</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>نیسان</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>خمام</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>1400000</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>1600000</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>خشکبیجار</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>1050000</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>1400000</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>خلیف محله شلمان</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>400000</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>550000</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>700000</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>خالکیاسر</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>330000</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>450000</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>600000</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>خاله سرا اطاقور</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>520000</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>700000</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>880000</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>خاله جیر شلمان</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>380000</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>520000</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>680000</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>خراط محله</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>300000</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>420000</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>570000</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>خرما</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>740000</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>910000</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>1100000</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>خرم آباد</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>880000</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>950000</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>1050000</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>خرم آباد تنکابن</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="n">
-        <v>1650000</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>1850000</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>2050000</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>خرشتم</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="n">
-        <v>550000</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>720000</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>900000</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>